--- a/Fase 2/Evidencias Grupales/Diccionario_de_datos_escuela_conductores.xlsx
+++ b/Fase 2/Evidencias Grupales/Diccionario_de_datos_escuela_conductores.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Gabriel\Documents\Codex\2026-10-17\hola-chat-necesito-que-x20\outputs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2b680ed20cb65f7b/Documentos/QA/capstone/Fase 2/Evidencias Grupales/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BA8CCF6-D374-4693-9AD6-19F0F06A0023}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{0BA8CCF6-D374-4693-9AD6-19F0F06A0023}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3DABE2C2-CF32-446A-9C4F-6B1134DB6033}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="330" windowWidth="29040" windowHeight="15990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tablas" sheetId="1" r:id="rId1"/>
@@ -20,16 +20,11 @@
     <sheet name="Notas" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="0"/>
-  <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1033" uniqueCount="254">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1029" uniqueCount="250">
   <si>
     <t>Diccionario de datos · escuela_conductores</t>
   </si>
@@ -136,9 +131,6 @@
     <t>Definición de campos</t>
   </si>
   <si>
-    <t>Fuente: script_base_datos.sql · PK: clave primaria; FK: clave foránea; UQ: único.</t>
-  </si>
-  <si>
     <t>Campo</t>
   </si>
   <si>
@@ -514,9 +506,6 @@
     <t>Relaciones entre tablas</t>
   </si>
   <si>
-    <t>Cardinalidad desde la tabla referenciada hacia el origen; obligatoriedad desde el registro de origen.</t>
-  </si>
-  <si>
     <t>Restricción</t>
   </si>
   <si>
@@ -610,9 +599,6 @@
     <t>Claves e índices</t>
   </si>
   <si>
-    <t>Restricciones e índices declarados explícitamente en el SQL.</t>
-  </si>
-  <si>
     <t>Nombre</t>
   </si>
   <si>
@@ -697,9 +683,6 @@
     <t>Alcance y criterios de lectura</t>
   </si>
   <si>
-    <t>Fuente y límites de interpretación del diccionario.</t>
-  </si>
-  <si>
     <t>Concepto</t>
   </si>
   <si>
@@ -715,9 +698,6 @@
     <t>Fuente SQL</t>
   </si>
   <si>
-    <t>D:/DUOC/CAPSTONE/codigo/capstone/Fase 2/Evidencias Grupales/script_base_datos.sql</t>
-  </si>
-  <si>
     <t>Fecha de elaboración</t>
   </si>
   <si>
@@ -791,6 +771,9 @@
   </si>
   <si>
     <t>VARCHAR: longitud en caracteres; DECIMAL: precisión y escala; TINYINT(1) no restringe por sí solo los valores a 0 y 1.</t>
+  </si>
+  <si>
+    <t>script_base_datos.sql</t>
   </si>
 </sst>
 </file>
@@ -857,15 +840,15 @@
   </cellStyleXfs>
   <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1371,40 +1354,38 @@
       </c>
     </row>
     <row r="3" spans="1:10">
-      <c r="A3" s="2" t="s">
-        <v>35</v>
-      </c>
+      <c r="A3" s="2"/>
     </row>
     <row r="5" spans="1:10" ht="32.1" customHeight="1">
       <c r="A5" s="5" t="s">
         <v>2</v>
       </c>
       <c r="B5" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C5" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="D5" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="E5" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="F5" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="G5" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="G5" s="5" t="s">
+      <c r="H5" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="H5" s="5" t="s">
+      <c r="I5" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="I5" s="5" t="s">
+      <c r="J5" s="5" t="s">
         <v>43</v>
-      </c>
-      <c r="J5" s="5" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="48" customHeight="1">
@@ -1415,28 +1396,28 @@
         <v>9</v>
       </c>
       <c r="C6" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D6" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="E6" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="E6" s="3" t="s">
-        <v>47</v>
-      </c>
       <c r="F6" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G6" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H6" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="H6" s="3" t="s">
+      <c r="I6" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="I6" s="3" t="s">
-        <v>51</v>
-      </c>
       <c r="J6" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="48" customHeight="1">
@@ -1444,31 +1425,31 @@
         <v>7</v>
       </c>
       <c r="B7" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C7" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="D7" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="E7" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="F7" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="H7" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="F7" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="H7" s="4" t="s">
-        <v>57</v>
-      </c>
       <c r="I7" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="48" customHeight="1">
@@ -1479,28 +1460,28 @@
         <v>13</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D8" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E8" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="E8" s="3" t="s">
-        <v>47</v>
-      </c>
       <c r="F8" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G8" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H8" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="H8" s="3" t="s">
+      <c r="I8" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="I8" s="3" t="s">
-        <v>51</v>
-      </c>
       <c r="J8" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="48" customHeight="1">
@@ -1508,31 +1489,31 @@
         <v>11</v>
       </c>
       <c r="B9" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="C9" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="D9" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="E9" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="E9" s="4" t="s">
-        <v>62</v>
-      </c>
       <c r="F9" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="48" customHeight="1">
@@ -1540,31 +1521,31 @@
         <v>11</v>
       </c>
       <c r="B10" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="D10" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="E10" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="E10" s="3" t="s">
-        <v>66</v>
-      </c>
       <c r="F10" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="48" customHeight="1">
@@ -1572,31 +1553,31 @@
         <v>11</v>
       </c>
       <c r="B11" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C11" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="D11" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="E11" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="E11" s="4" t="s">
-        <v>70</v>
-      </c>
       <c r="F11" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="48" customHeight="1">
@@ -1604,31 +1585,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="D12" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="E12" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="G12" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="E12" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>74</v>
-      </c>
       <c r="H12" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="48" customHeight="1">
@@ -1639,28 +1620,28 @@
         <v>16</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D13" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E13" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="E13" s="4" t="s">
-        <v>47</v>
-      </c>
       <c r="F13" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G13" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="H13" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="H13" s="4" t="s">
+      <c r="I13" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="I13" s="4" t="s">
-        <v>51</v>
-      </c>
       <c r="J13" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="48" customHeight="1">
@@ -1668,31 +1649,31 @@
         <v>14</v>
       </c>
       <c r="B14" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="D14" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="E14" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>79</v>
-      </c>
       <c r="F14" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="48" customHeight="1">
@@ -1700,31 +1681,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C15" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="C15" s="4" t="s">
-        <v>81</v>
-      </c>
       <c r="D15" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="E15" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="E15" s="4" t="s">
-        <v>62</v>
-      </c>
       <c r="F15" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J15" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="48" customHeight="1">
@@ -1732,31 +1713,31 @@
         <v>14</v>
       </c>
       <c r="B16" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="C16" s="3" t="s">
-        <v>83</v>
-      </c>
       <c r="D16" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="E16" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="E16" s="3" t="s">
-        <v>70</v>
-      </c>
       <c r="F16" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="48" customHeight="1">
@@ -1767,28 +1748,28 @@
         <v>13</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D17" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E17" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="E17" s="4" t="s">
-        <v>47</v>
-      </c>
       <c r="F17" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H17" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="I17" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="J17" s="4" t="s">
         <v>84</v>
-      </c>
-      <c r="I17" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="J17" s="4" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="48" customHeight="1">
@@ -1796,31 +1777,31 @@
         <v>14</v>
       </c>
       <c r="B18" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="C18" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="D18" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="D18" s="3" t="s">
+      <c r="E18" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="E18" s="3" t="s">
-        <v>89</v>
-      </c>
       <c r="F18" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="48" customHeight="1">
@@ -1828,31 +1809,31 @@
         <v>14</v>
       </c>
       <c r="B19" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="C19" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="D19" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="E19" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="G19" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="E19" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="F19" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="G19" s="4" t="s">
-        <v>74</v>
-      </c>
       <c r="H19" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I19" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J19" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="48" customHeight="1">
@@ -1863,28 +1844,28 @@
         <v>19</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D20" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E20" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="E20" s="3" t="s">
-        <v>47</v>
-      </c>
       <c r="F20" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G20" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H20" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="H20" s="3" t="s">
+      <c r="I20" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="I20" s="3" t="s">
-        <v>51</v>
-      </c>
       <c r="J20" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="48" customHeight="1">
@@ -1892,31 +1873,31 @@
         <v>17</v>
       </c>
       <c r="B21" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="C21" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="C21" s="4" t="s">
+      <c r="D21" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="D21" s="4" t="s">
+      <c r="E21" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="E21" s="4" t="s">
-        <v>94</v>
-      </c>
       <c r="F21" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I21" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J21" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="48" customHeight="1">
@@ -1924,31 +1905,31 @@
         <v>17</v>
       </c>
       <c r="B22" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C22" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="D22" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="D22" s="3" t="s">
+      <c r="E22" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="E22" s="3" t="s">
-        <v>62</v>
-      </c>
       <c r="F22" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="48" customHeight="1">
@@ -1956,31 +1937,31 @@
         <v>17</v>
       </c>
       <c r="B23" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="C23" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="C23" s="4" t="s">
-        <v>96</v>
-      </c>
       <c r="D23" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="E23" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="E23" s="4" t="s">
-        <v>62</v>
-      </c>
       <c r="F23" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I23" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J23" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="24" spans="1:10" ht="48" customHeight="1">
@@ -1988,31 +1969,31 @@
         <v>17</v>
       </c>
       <c r="B24" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C24" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="D24" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="D24" s="3" t="s">
+      <c r="E24" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="E24" s="3" t="s">
-        <v>100</v>
-      </c>
       <c r="F24" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="25" spans="1:10" ht="48" customHeight="1">
@@ -2020,31 +2001,31 @@
         <v>17</v>
       </c>
       <c r="B25" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="C25" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="C25" s="4" t="s">
-        <v>102</v>
-      </c>
       <c r="D25" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E25" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="E25" s="4" t="s">
-        <v>66</v>
-      </c>
       <c r="F25" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I25" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J25" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="26" spans="1:10" ht="48" customHeight="1">
@@ -2055,28 +2036,28 @@
         <v>9</v>
       </c>
       <c r="C26" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D26" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="D26" s="3" t="s">
+      <c r="E26" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="E26" s="3" t="s">
-        <v>47</v>
-      </c>
       <c r="F26" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="27" spans="1:10" ht="48" customHeight="1">
@@ -2087,28 +2068,28 @@
         <v>13</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D27" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E27" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="E27" s="4" t="s">
-        <v>47</v>
-      </c>
       <c r="F27" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H27" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="I27" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="J27" s="4" t="s">
         <v>84</v>
-      </c>
-      <c r="I27" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="J27" s="4" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="28" spans="1:10" ht="48" customHeight="1">
@@ -2116,31 +2097,31 @@
         <v>17</v>
       </c>
       <c r="B28" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="C28" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="C28" s="3" t="s">
+      <c r="D28" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="D28" s="3" t="s">
+      <c r="E28" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="E28" s="3" t="s">
-        <v>107</v>
-      </c>
       <c r="F28" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="29" spans="1:10" ht="48" customHeight="1">
@@ -2148,31 +2129,31 @@
         <v>17</v>
       </c>
       <c r="B29" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="C29" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="C29" s="4" t="s">
+      <c r="D29" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="D29" s="4" t="s">
+      <c r="E29" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="G29" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="E29" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="F29" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="G29" s="4" t="s">
-        <v>74</v>
-      </c>
       <c r="H29" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I29" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J29" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="30" spans="1:10" ht="48" customHeight="1">
@@ -2183,28 +2164,28 @@
         <v>19</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D30" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E30" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="E30" s="3" t="s">
-        <v>47</v>
-      </c>
       <c r="F30" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H30" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="I30" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="J30" s="3" t="s">
         <v>108</v>
-      </c>
-      <c r="I30" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="J30" s="3" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="31" spans="1:10" ht="48" customHeight="1">
@@ -2212,31 +2193,31 @@
         <v>20</v>
       </c>
       <c r="B31" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="C31" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="C31" s="4" t="s">
-        <v>111</v>
-      </c>
       <c r="D31" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="E31" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="E31" s="4" t="s">
-        <v>89</v>
-      </c>
       <c r="F31" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H31" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I31" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J31" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="32" spans="1:10" ht="48" customHeight="1">
@@ -2244,31 +2225,31 @@
         <v>20</v>
       </c>
       <c r="B32" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C32" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="C32" s="3" t="s">
+      <c r="D32" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>114</v>
-      </c>
       <c r="E32" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="33" spans="1:10" ht="48" customHeight="1">
@@ -2276,31 +2257,31 @@
         <v>20</v>
       </c>
       <c r="B33" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="C33" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="C33" s="4" t="s">
+      <c r="D33" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="D33" s="4" t="s">
-        <v>117</v>
-      </c>
       <c r="E33" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G33" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H33" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I33" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J33" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="34" spans="1:10" ht="48" customHeight="1">
@@ -2308,31 +2289,31 @@
         <v>20</v>
       </c>
       <c r="B34" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="C34" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="C34" s="3" t="s">
+      <c r="D34" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="D34" s="3" t="s">
+      <c r="E34" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="E34" s="3" t="s">
+      <c r="F34" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="G34" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="F34" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="G34" s="3" t="s">
-        <v>122</v>
-      </c>
       <c r="H34" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="35" spans="1:10" ht="48" customHeight="1">
@@ -2340,31 +2321,31 @@
         <v>20</v>
       </c>
       <c r="B35" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="C35" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="C35" s="4" t="s">
-        <v>124</v>
-      </c>
       <c r="D35" s="4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H35" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I35" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J35" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="36" spans="1:10" ht="48" customHeight="1">
@@ -2375,28 +2356,28 @@
         <v>24</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D36" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E36" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="E36" s="3" t="s">
-        <v>47</v>
-      </c>
       <c r="F36" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G36" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H36" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="H36" s="3" t="s">
+      <c r="I36" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="I36" s="3" t="s">
-        <v>51</v>
-      </c>
       <c r="J36" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="37" spans="1:10" ht="48" customHeight="1">
@@ -2404,31 +2385,31 @@
         <v>22</v>
       </c>
       <c r="B37" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="C37" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="C37" s="4" t="s">
-        <v>127</v>
-      </c>
       <c r="D37" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E37" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="E37" s="4" t="s">
-        <v>47</v>
-      </c>
       <c r="F37" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G37" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H37" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I37" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J37" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="38" spans="1:10" ht="48" customHeight="1">
@@ -2436,31 +2417,31 @@
         <v>22</v>
       </c>
       <c r="B38" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="C38" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="C38" s="3" t="s">
-        <v>129</v>
-      </c>
       <c r="D38" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E38" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="E38" s="3" t="s">
-        <v>47</v>
-      </c>
       <c r="F38" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="39" spans="1:10" ht="48" customHeight="1">
@@ -2468,31 +2449,31 @@
         <v>22</v>
       </c>
       <c r="B39" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="C39" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="C39" s="4" t="s">
-        <v>131</v>
-      </c>
       <c r="D39" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="E39" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="E39" s="4" t="s">
-        <v>56</v>
-      </c>
       <c r="F39" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G39" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H39" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I39" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J39" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="40" spans="1:10" ht="48" customHeight="1">
@@ -2500,31 +2481,31 @@
         <v>22</v>
       </c>
       <c r="B40" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="C40" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="C40" s="3" t="s">
+      <c r="D40" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="D40" s="3" t="s">
+      <c r="E40" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="E40" s="3" t="s">
-        <v>135</v>
-      </c>
       <c r="F40" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="41" spans="1:10" ht="48" customHeight="1">
@@ -2532,31 +2513,31 @@
         <v>22</v>
       </c>
       <c r="B41" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="C41" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="C41" s="4" t="s">
-        <v>137</v>
-      </c>
       <c r="D41" s="4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G41" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H41" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I41" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J41" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="42" spans="1:10" ht="48" customHeight="1">
@@ -2564,31 +2545,31 @@
         <v>22</v>
       </c>
       <c r="B42" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="C42" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="C42" s="3" t="s">
-        <v>139</v>
-      </c>
       <c r="D42" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="43" spans="1:10" ht="48" customHeight="1">
@@ -2596,31 +2577,31 @@
         <v>22</v>
       </c>
       <c r="B43" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="C43" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="C43" s="4" t="s">
+      <c r="D43" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="D43" s="4" t="s">
+      <c r="E43" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="F43" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="G43" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="E43" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="F43" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="G43" s="4" t="s">
-        <v>74</v>
-      </c>
       <c r="H43" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I43" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J43" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="44" spans="1:10" ht="48" customHeight="1">
@@ -2631,28 +2612,28 @@
         <v>27</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D44" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E44" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="E44" s="3" t="s">
-        <v>47</v>
-      </c>
       <c r="F44" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G44" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H44" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="H44" s="3" t="s">
+      <c r="I44" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="I44" s="3" t="s">
-        <v>51</v>
-      </c>
       <c r="J44" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="45" spans="1:10" ht="48" customHeight="1">
@@ -2660,31 +2641,31 @@
         <v>25</v>
       </c>
       <c r="B45" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="C45" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="C45" s="4" t="s">
-        <v>127</v>
-      </c>
       <c r="D45" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E45" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="E45" s="4" t="s">
-        <v>47</v>
-      </c>
       <c r="F45" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G45" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H45" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I45" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J45" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="46" spans="1:10" ht="48" customHeight="1">
@@ -2692,31 +2673,31 @@
         <v>25</v>
       </c>
       <c r="B46" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="C46" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="C46" s="3" t="s">
-        <v>129</v>
-      </c>
       <c r="D46" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E46" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="E46" s="3" t="s">
-        <v>47</v>
-      </c>
       <c r="F46" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="47" spans="1:10" ht="48" customHeight="1">
@@ -2724,31 +2705,31 @@
         <v>25</v>
       </c>
       <c r="B47" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="C47" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="C47" s="4" t="s">
-        <v>142</v>
-      </c>
       <c r="D47" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="E47" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="E47" s="4" t="s">
-        <v>62</v>
-      </c>
       <c r="F47" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G47" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H47" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I47" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J47" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="48" spans="1:10" ht="48" customHeight="1">
@@ -2756,31 +2737,31 @@
         <v>25</v>
       </c>
       <c r="B48" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C48" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="C48" s="3" t="s">
-        <v>137</v>
-      </c>
       <c r="D48" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="49" spans="1:10" ht="48" customHeight="1">
@@ -2788,31 +2769,31 @@
         <v>25</v>
       </c>
       <c r="B49" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="C49" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="C49" s="4" t="s">
-        <v>144</v>
-      </c>
       <c r="D49" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="E49" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="E49" s="4" t="s">
-        <v>70</v>
-      </c>
       <c r="F49" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G49" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H49" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I49" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J49" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="50" spans="1:10" ht="48" customHeight="1">
@@ -2820,31 +2801,31 @@
         <v>25</v>
       </c>
       <c r="B50" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="C50" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="C50" s="3" t="s">
-        <v>146</v>
-      </c>
       <c r="D50" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F50" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="G50" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="E50" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="F50" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="G50" s="3" t="s">
-        <v>74</v>
-      </c>
       <c r="H50" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="51" spans="1:10" ht="48" customHeight="1">
@@ -2855,28 +2836,28 @@
         <v>30</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D51" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E51" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="E51" s="4" t="s">
-        <v>47</v>
-      </c>
       <c r="F51" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G51" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="H51" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="H51" s="4" t="s">
+      <c r="I51" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="I51" s="4" t="s">
-        <v>51</v>
-      </c>
       <c r="J51" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="52" spans="1:10" ht="48" customHeight="1">
@@ -2887,28 +2868,28 @@
         <v>16</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D52" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E52" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="E52" s="3" t="s">
-        <v>47</v>
-      </c>
       <c r="F52" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="53" spans="1:10" ht="48" customHeight="1">
@@ -2916,31 +2897,31 @@
         <v>28</v>
       </c>
       <c r="B53" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="C53" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="C53" s="4" t="s">
-        <v>129</v>
-      </c>
       <c r="D53" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E53" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="E53" s="4" t="s">
-        <v>47</v>
-      </c>
       <c r="F53" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G53" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H53" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I53" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J53" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="54" spans="1:10" ht="48" customHeight="1">
@@ -2948,31 +2929,31 @@
         <v>28</v>
       </c>
       <c r="B54" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C54" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="C54" s="3" t="s">
-        <v>137</v>
-      </c>
       <c r="D54" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="55" spans="1:10" ht="48" customHeight="1">
@@ -2980,31 +2961,31 @@
         <v>28</v>
       </c>
       <c r="B55" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="C55" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="C55" s="4" t="s">
+      <c r="D55" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="D55" s="4" t="s">
+      <c r="E55" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="E55" s="4" t="s">
-        <v>152</v>
-      </c>
       <c r="F55" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G55" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H55" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I55" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J55" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="56" spans="1:10" ht="48" customHeight="1">
@@ -3012,31 +2993,31 @@
         <v>28</v>
       </c>
       <c r="B56" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="C56" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="C56" s="3" t="s">
-        <v>154</v>
-      </c>
       <c r="D56" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="E56" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="E56" s="3" t="s">
-        <v>152</v>
-      </c>
       <c r="F56" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G56" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J56" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="57" spans="1:10" ht="48" customHeight="1">
@@ -3044,31 +3025,31 @@
         <v>28</v>
       </c>
       <c r="B57" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="C57" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="C57" s="4" t="s">
-        <v>156</v>
-      </c>
       <c r="D57" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E57" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="E57" s="4" t="s">
-        <v>66</v>
-      </c>
       <c r="F57" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G57" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H57" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I57" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J57" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="58" spans="1:10" ht="48" customHeight="1">
@@ -3076,31 +3057,31 @@
         <v>28</v>
       </c>
       <c r="B58" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C58" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="C58" s="3" t="s">
+      <c r="D58" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="D58" s="3" t="s">
+      <c r="E58" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F58" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="G58" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="E58" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="F58" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="G58" s="3" t="s">
-        <v>74</v>
-      </c>
       <c r="H58" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J58" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="59" spans="1:10" ht="48" customHeight="1">
@@ -3111,28 +3092,28 @@
         <v>33</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D59" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E59" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="E59" s="4" t="s">
-        <v>47</v>
-      </c>
       <c r="F59" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G59" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="H59" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="H59" s="4" t="s">
+      <c r="I59" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="I59" s="4" t="s">
-        <v>51</v>
-      </c>
       <c r="J59" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="60" spans="1:10" ht="48" customHeight="1">
@@ -3140,31 +3121,31 @@
         <v>31</v>
       </c>
       <c r="B60" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="C60" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="C60" s="3" t="s">
-        <v>127</v>
-      </c>
       <c r="D60" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E60" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="E60" s="3" t="s">
-        <v>47</v>
-      </c>
       <c r="F60" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J60" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="61" spans="1:10" ht="48" customHeight="1">
@@ -3172,31 +3153,31 @@
         <v>31</v>
       </c>
       <c r="B61" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="C61" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="C61" s="4" t="s">
-        <v>129</v>
-      </c>
       <c r="D61" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E61" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="E61" s="4" t="s">
-        <v>47</v>
-      </c>
       <c r="F61" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G61" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H61" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I61" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J61" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="62" spans="1:10" ht="48" customHeight="1">
@@ -3207,28 +3188,28 @@
         <v>16</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D62" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E62" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="E62" s="3" t="s">
-        <v>47</v>
-      </c>
       <c r="F62" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G62" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J62" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="63" spans="1:10" ht="48" customHeight="1">
@@ -3239,28 +3220,28 @@
         <v>13</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D63" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E63" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="E63" s="4" t="s">
-        <v>47</v>
-      </c>
       <c r="F63" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G63" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H63" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="I63" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="J63" s="4" t="s">
         <v>84</v>
-      </c>
-      <c r="I63" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="J63" s="4" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="64" spans="1:10" ht="48" customHeight="1">
@@ -3268,31 +3249,31 @@
         <v>31</v>
       </c>
       <c r="B64" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C64" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="C64" s="3" t="s">
-        <v>137</v>
-      </c>
       <c r="D64" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G64" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J64" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="65" spans="1:10" ht="48" customHeight="1">
@@ -3300,31 +3281,31 @@
         <v>31</v>
       </c>
       <c r="B65" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="C65" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="C65" s="4" t="s">
+      <c r="D65" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="D65" s="4" t="s">
+      <c r="E65" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="E65" s="4" t="s">
-        <v>152</v>
-      </c>
       <c r="F65" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G65" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H65" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I65" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J65" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="66" spans="1:10" ht="48" customHeight="1">
@@ -3332,31 +3313,31 @@
         <v>31</v>
       </c>
       <c r="B66" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="C66" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="C66" s="3" t="s">
-        <v>154</v>
-      </c>
       <c r="D66" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="E66" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="E66" s="3" t="s">
-        <v>152</v>
-      </c>
       <c r="F66" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G66" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J66" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="67" spans="1:10" ht="48" customHeight="1">
@@ -3364,31 +3345,31 @@
         <v>31</v>
       </c>
       <c r="B67" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="C67" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="C67" s="4" t="s">
-        <v>144</v>
-      </c>
       <c r="D67" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="E67" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="E67" s="4" t="s">
-        <v>89</v>
-      </c>
       <c r="F67" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G67" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H67" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I67" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J67" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="68" spans="1:10" ht="48" customHeight="1">
@@ -3396,31 +3377,31 @@
         <v>31</v>
       </c>
       <c r="B68" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="C68" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="C68" s="3" t="s">
-        <v>159</v>
-      </c>
       <c r="D68" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="E68" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="E68" s="3" t="s">
-        <v>62</v>
-      </c>
       <c r="F68" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G68" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J68" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="69" spans="1:10" ht="48" customHeight="1">
@@ -3428,31 +3409,31 @@
         <v>31</v>
       </c>
       <c r="B69" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="C69" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="C69" s="4" t="s">
-        <v>139</v>
-      </c>
       <c r="D69" s="4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G69" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H69" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I69" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J69" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="70" spans="1:10" ht="48" customHeight="1">
@@ -3460,31 +3441,31 @@
         <v>31</v>
       </c>
       <c r="B70" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C70" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="C70" s="3" t="s">
+      <c r="D70" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="D70" s="3" t="s">
+      <c r="E70" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F70" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="G70" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="E70" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="F70" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="G70" s="3" t="s">
-        <v>74</v>
-      </c>
       <c r="H70" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J70" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -3511,46 +3492,44 @@
   <sheetData>
     <row r="2" spans="1:9" ht="18">
       <c r="A2" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="3" spans="1:9">
-      <c r="A3" s="2" t="s">
-        <v>161</v>
-      </c>
+      <c r="A3" s="2"/>
     </row>
     <row r="5" spans="1:9" ht="32.1" customHeight="1">
       <c r="A5" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="C5" s="5" t="s">
         <v>162</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="D5" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="E5" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="F5" s="5" t="s">
         <v>165</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="G5" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="H5" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="G5" s="5" t="s">
+      <c r="I5" s="5" t="s">
         <v>168</v>
-      </c>
-      <c r="H5" s="5" t="s">
-        <v>169</v>
-      </c>
-      <c r="I5" s="5" t="s">
-        <v>170</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="48" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>14</v>
@@ -3565,21 +3544,21 @@
         <v>13</v>
       </c>
       <c r="F6" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="H6" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="G6" s="3" t="s">
+      <c r="I6" s="3" t="s">
         <v>173</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="48" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>17</v>
@@ -3594,21 +3573,21 @@
         <v>9</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="48" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>17</v>
@@ -3623,21 +3602,21 @@
         <v>13</v>
       </c>
       <c r="F8" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="H8" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="G8" s="3" t="s">
+      <c r="I8" s="3" t="s">
         <v>173</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="48" customHeight="1">
       <c r="A9" s="4" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>20</v>
@@ -3652,27 +3631,27 @@
         <v>19</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="48" customHeight="1">
       <c r="A10" s="3" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>22</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>17</v>
@@ -3681,27 +3660,27 @@
         <v>19</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="48" customHeight="1">
       <c r="A11" s="4" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>22</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>17</v>
@@ -3710,27 +3689,27 @@
         <v>19</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="48" customHeight="1">
       <c r="A12" s="3" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>25</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>17</v>
@@ -3739,27 +3718,27 @@
         <v>19</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="48" customHeight="1">
       <c r="A13" s="4" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>25</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>17</v>
@@ -3768,21 +3747,21 @@
         <v>19</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="48" customHeight="1">
       <c r="A14" s="3" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>28</v>
@@ -3797,27 +3776,27 @@
         <v>16</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="48" customHeight="1">
       <c r="A15" s="4" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>28</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>17</v>
@@ -3826,27 +3805,27 @@
         <v>19</v>
       </c>
       <c r="F15" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="H15" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="G15" s="4" t="s">
+      <c r="I15" s="4" t="s">
         <v>173</v>
-      </c>
-      <c r="H15" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="I15" s="4" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="48" customHeight="1">
       <c r="A16" s="3" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>17</v>
@@ -3855,27 +3834,27 @@
         <v>19</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="48" customHeight="1">
       <c r="A17" s="4" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>31</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D17" s="4" t="s">
         <v>17</v>
@@ -3884,21 +3863,21 @@
         <v>19</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="I17" s="4" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="48" customHeight="1">
       <c r="A18" s="3" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>31</v>
@@ -3913,21 +3892,21 @@
         <v>16</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="48" customHeight="1">
       <c r="A19" s="4" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>31</v>
@@ -3942,16 +3921,16 @@
         <v>13</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="I19" s="4" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
   </sheetData>
@@ -3976,29 +3955,27 @@
   <sheetData>
     <row r="2" spans="1:5" ht="18">
       <c r="A2" s="1" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="2" t="s">
-        <v>193</v>
-      </c>
+      <c r="A3" s="2"/>
     </row>
     <row r="5" spans="1:5" ht="32.1" customHeight="1">
       <c r="A5" s="5" t="s">
         <v>2</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>4</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="48" customHeight="1">
@@ -4006,16 +3983,16 @@
         <v>7</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>9</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="48" customHeight="1">
@@ -4023,16 +4000,16 @@
         <v>7</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="48" customHeight="1">
@@ -4040,16 +4017,16 @@
         <v>11</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>13</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="48" customHeight="1">
@@ -4057,16 +4034,16 @@
         <v>14</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>16</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="48" customHeight="1">
@@ -4074,16 +4051,16 @@
         <v>14</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="48" customHeight="1">
@@ -4091,16 +4068,16 @@
         <v>14</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="48" customHeight="1">
@@ -4108,16 +4085,16 @@
         <v>17</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>19</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="48" customHeight="1">
@@ -4125,16 +4102,16 @@
         <v>17</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="48" customHeight="1">
@@ -4142,16 +4119,16 @@
         <v>17</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="48" customHeight="1">
@@ -4159,16 +4136,16 @@
         <v>17</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>9</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="48" customHeight="1">
@@ -4176,16 +4153,16 @@
         <v>17</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>13</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="48" customHeight="1">
@@ -4193,16 +4170,16 @@
         <v>20</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="D17" s="4" t="s">
         <v>19</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="48" customHeight="1">
@@ -4210,16 +4187,16 @@
         <v>20</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>19</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="48" customHeight="1">
@@ -4227,16 +4204,16 @@
         <v>22</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="D19" s="4" t="s">
         <v>24</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="48" customHeight="1">
@@ -4244,16 +4221,16 @@
         <v>22</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="48" customHeight="1">
@@ -4261,16 +4238,16 @@
         <v>22</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="48" customHeight="1">
@@ -4278,16 +4255,16 @@
         <v>25</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>27</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="48" customHeight="1">
@@ -4295,16 +4272,16 @@
         <v>25</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="48" customHeight="1">
@@ -4312,16 +4289,16 @@
         <v>25</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="48" customHeight="1">
@@ -4329,16 +4306,16 @@
         <v>28</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="D25" s="4" t="s">
         <v>30</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="48" customHeight="1">
@@ -4346,16 +4323,16 @@
         <v>28</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>16</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="48" customHeight="1">
@@ -4363,16 +4340,16 @@
         <v>28</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="48" customHeight="1">
@@ -4380,16 +4357,16 @@
         <v>28</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="48" customHeight="1">
@@ -4397,16 +4374,16 @@
         <v>31</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="D29" s="4" t="s">
         <v>33</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="48" customHeight="1">
@@ -4414,16 +4391,16 @@
         <v>31</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="48" customHeight="1">
@@ -4431,16 +4408,16 @@
         <v>31</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="48" customHeight="1">
@@ -4448,16 +4425,16 @@
         <v>31</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="48" customHeight="1">
@@ -4465,16 +4442,16 @@
         <v>31</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="D33" s="4" t="s">
         <v>16</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="48" customHeight="1">
@@ -4482,16 +4459,16 @@
         <v>31</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>13</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="48" customHeight="1">
@@ -4499,16 +4476,16 @@
         <v>31</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
     </row>
   </sheetData>
@@ -4530,140 +4507,138 @@
   <sheetData>
     <row r="2" spans="1:2" ht="18">
       <c r="A2" s="1" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" s="2" t="s">
-        <v>222</v>
-      </c>
+      <c r="A3" s="2"/>
     </row>
     <row r="5" spans="1:2" ht="32.1" customHeight="1">
       <c r="A5" s="5" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="48" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="48" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>228</v>
+        <v>249</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="48" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="48" customHeight="1">
       <c r="A9" s="4" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="48" customHeight="1">
       <c r="A10" s="3" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="48" customHeight="1">
       <c r="A11" s="4" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="48" customHeight="1">
       <c r="A12" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="48" customHeight="1">
       <c r="A13" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="48" customHeight="1">
       <c r="A14" s="3" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="48" customHeight="1">
       <c r="A15" s="4" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="48" customHeight="1">
       <c r="A16" s="3" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="48" customHeight="1">
       <c r="A17" s="4" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="48" customHeight="1">
       <c r="A18" s="3" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="48" customHeight="1">
       <c r="A19" s="4" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="48" customHeight="1">
       <c r="A20" s="3" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
     </row>
   </sheetData>
